--- a/files/01_Rivanta_TechBudgetVariance.xlsx
+++ b/files/01_Rivanta_TechBudgetVariance.xlsx
@@ -53,7 +53,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="0092400E"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,7 +61,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00991B1B"/>
     </font>
   </fonts>
   <fills count="7">
@@ -78,7 +78,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,7 +88,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,10 +138,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,6 +221,81 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CostCentres" displayName="CostCentres" ref="A1:D13" headerRowCount="1">
+  <autoFilter ref="A1:D13"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Cost Centre Code"/>
+    <tableColumn id="2" name="Cost Centre"/>
+    <tableColumn id="3" name="Pillar"/>
+    <tableColumn id="4" name="Owner / Head"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MonthlyPnL" displayName="MonthlyPnL" ref="A1:AH13" headerRowCount="1">
+  <autoFilter ref="A1:AH13"/>
+  <tableColumns count="34">
+    <tableColumn id="1" name="Cost Centre Code"/>
+    <tableColumn id="2" name="Cost Centre"/>
+    <tableColumn id="3" name="Pillar"/>
+    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="5" name="Annual Budget (RM '000)"/>
+    <tableColumn id="6" name="Budget Jan"/>
+    <tableColumn id="7" name="Actual Jan"/>
+    <tableColumn id="8" name="Budget Feb"/>
+    <tableColumn id="9" name="Actual Feb"/>
+    <tableColumn id="10" name="Budget Mar"/>
+    <tableColumn id="11" name="Actual Mar"/>
+    <tableColumn id="12" name="Budget Apr"/>
+    <tableColumn id="13" name="Actual Apr"/>
+    <tableColumn id="14" name="Budget May"/>
+    <tableColumn id="15" name="Actual May"/>
+    <tableColumn id="16" name="Budget Jun"/>
+    <tableColumn id="17" name="Actual Jun"/>
+    <tableColumn id="18" name="Budget Jul"/>
+    <tableColumn id="19" name="Actual Jul"/>
+    <tableColumn id="20" name="Budget Aug"/>
+    <tableColumn id="21" name="Actual Aug"/>
+    <tableColumn id="22" name="Budget Sep"/>
+    <tableColumn id="23" name="Actual Sep"/>
+    <tableColumn id="24" name="Budget Oct"/>
+    <tableColumn id="25" name="Actual Oct"/>
+    <tableColumn id="26" name="Budget Nov"/>
+    <tableColumn id="27" name="Actual Nov"/>
+    <tableColumn id="28" name="Budget Dec"/>
+    <tableColumn id="29" name="Actual Dec"/>
+    <tableColumn id="30" name="YTD Budget"/>
+    <tableColumn id="31" name="YTD Actual"/>
+    <tableColumn id="32" name="YTD Variance"/>
+    <tableColumn id="33" name="Variance %"/>
+    <tableColumn id="34" name="RAG"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ProjectStatus" displayName="ProjectStatus" ref="A1:J11" headerRowCount="1">
+  <autoFilter ref="A1:J11"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Project Code"/>
+    <tableColumn id="2" name="Project Name"/>
+    <tableColumn id="3" name="Sponsor"/>
+    <tableColumn id="4" name="Pillar"/>
+    <tableColumn id="5" name="Approved Budget (RM '000)"/>
+    <tableColumn id="6" name="Spent to Date (RM '000)"/>
+    <tableColumn id="7" name="Forecast at Completion (RM '000)"/>
+    <tableColumn id="8" name="Schedule Status"/>
+    <tableColumn id="9" name="Risk Rating"/>
+    <tableColumn id="10" name="Comment"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,7 +625,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reporting period: Jan 2026 – Dec 2026 (with full-year forecast)</t>
+          <t>Reporting period: Q1 FY2026 (1 Jan – 31 Mar 2026). FY2026 full-year budget shown for context.</t>
         </is>
       </c>
     </row>
@@ -918,6 +993,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1183,72 +1261,45 @@
       <c r="L2" s="6" t="n">
         <v>2370.4</v>
       </c>
-      <c r="M2" s="6" t="n">
-        <v>2607.4</v>
-      </c>
       <c r="N2" s="6" t="n">
         <v>2370.4</v>
       </c>
-      <c r="O2" s="6" t="n">
-        <v>2702.3</v>
-      </c>
       <c r="P2" s="6" t="n">
         <v>2488.9</v>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v>2936.9</v>
-      </c>
       <c r="R2" s="6" t="n">
         <v>2370.4</v>
       </c>
-      <c r="S2" s="6" t="n">
-        <v>2844.5</v>
-      </c>
       <c r="T2" s="6" t="n">
         <v>2370.4</v>
       </c>
-      <c r="U2" s="6" t="n">
-        <v>2891.9</v>
-      </c>
       <c r="V2" s="6" t="n">
         <v>2488.9</v>
       </c>
-      <c r="W2" s="6" t="n">
-        <v>2936.9</v>
-      </c>
       <c r="X2" s="6" t="n">
         <v>2370.4</v>
       </c>
-      <c r="Y2" s="6" t="n">
-        <v>2726</v>
-      </c>
       <c r="Z2" s="6" t="n">
         <v>2370.4</v>
       </c>
-      <c r="AA2" s="6" t="n">
-        <v>2654.8</v>
-      </c>
       <c r="AB2" s="6" t="n">
         <v>2488.9</v>
       </c>
-      <c r="AC2" s="6" t="n">
-        <v>2737.8</v>
-      </c>
       <c r="AD2" s="6" t="n">
-        <v>28800.3</v>
+        <v>7111.2</v>
       </c>
       <c r="AE2" s="6" t="n">
-        <v>32508.8</v>
+        <v>7470.3</v>
       </c>
       <c r="AF2" s="6" t="n">
-        <v>3708.5</v>
+        <v>359.1</v>
       </c>
       <c r="AG2" s="7" t="n">
-        <v>0.1287660197984049</v>
+        <v>0.05049780627742154</v>
       </c>
       <c r="AH2" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Amber</t>
         </is>
       </c>
     </row>
@@ -1297,68 +1348,41 @@
       <c r="L3" s="6" t="n">
         <v>691.4</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>719.1</v>
-      </c>
       <c r="N3" s="6" t="n">
         <v>691.4</v>
       </c>
-      <c r="O3" s="6" t="n">
-        <v>726</v>
-      </c>
       <c r="P3" s="6" t="n">
         <v>725.9</v>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v>769.5</v>
-      </c>
       <c r="R3" s="6" t="n">
         <v>691.4</v>
       </c>
-      <c r="S3" s="6" t="n">
-        <v>726</v>
-      </c>
       <c r="T3" s="6" t="n">
         <v>691.4</v>
       </c>
-      <c r="U3" s="6" t="n">
-        <v>719.1</v>
-      </c>
       <c r="V3" s="6" t="n">
         <v>725.9</v>
       </c>
-      <c r="W3" s="6" t="n">
-        <v>747.7</v>
-      </c>
       <c r="X3" s="6" t="n">
         <v>691.4</v>
       </c>
-      <c r="Y3" s="6" t="n">
-        <v>705.2</v>
-      </c>
       <c r="Z3" s="6" t="n">
         <v>691.4</v>
       </c>
-      <c r="AA3" s="6" t="n">
-        <v>698.3</v>
-      </c>
       <c r="AB3" s="6" t="n">
         <v>725.9</v>
       </c>
-      <c r="AC3" s="6" t="n">
-        <v>725.9</v>
-      </c>
       <c r="AD3" s="6" t="n">
-        <v>8400.199999999999</v>
+        <v>2074.1</v>
       </c>
       <c r="AE3" s="6" t="n">
-        <v>8611.6</v>
+        <v>2074.8</v>
       </c>
       <c r="AF3" s="6" t="n">
-        <v>211.4</v>
+        <v>0.7</v>
       </c>
       <c r="AG3" s="7" t="n">
-        <v>0.02516606747458394</v>
+        <v>0.0003374957813027337</v>
       </c>
       <c r="AH3" s="9" t="inlineStr">
         <is>
@@ -1411,68 +1435,41 @@
       <c r="L4" s="6" t="n">
         <v>543.2</v>
       </c>
-      <c r="M4" s="6" t="n">
-        <v>554.1</v>
-      </c>
       <c r="N4" s="6" t="n">
         <v>543.2</v>
       </c>
-      <c r="O4" s="6" t="n">
-        <v>564.9</v>
-      </c>
       <c r="P4" s="6" t="n">
         <v>570.4</v>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v>598.9</v>
-      </c>
       <c r="R4" s="6" t="n">
         <v>543.2</v>
       </c>
-      <c r="S4" s="6" t="n">
-        <v>575.8</v>
-      </c>
       <c r="T4" s="6" t="n">
         <v>543.2</v>
       </c>
-      <c r="U4" s="6" t="n">
-        <v>581.2</v>
-      </c>
       <c r="V4" s="6" t="n">
         <v>570.4</v>
       </c>
-      <c r="W4" s="6" t="n">
-        <v>616</v>
-      </c>
       <c r="X4" s="6" t="n">
         <v>543.2</v>
       </c>
-      <c r="Y4" s="6" t="n">
-        <v>592.1</v>
-      </c>
       <c r="Z4" s="6" t="n">
         <v>543.2</v>
       </c>
-      <c r="AA4" s="6" t="n">
-        <v>597.5</v>
-      </c>
       <c r="AB4" s="6" t="n">
         <v>570.4</v>
       </c>
-      <c r="AC4" s="6" t="n">
-        <v>627.4</v>
-      </c>
       <c r="AD4" s="6" t="n">
-        <v>6600</v>
+        <v>1629.6</v>
       </c>
       <c r="AE4" s="6" t="n">
-        <v>6905.5</v>
+        <v>1597.6</v>
       </c>
       <c r="AF4" s="6" t="n">
-        <v>305.5</v>
+        <v>-32</v>
       </c>
       <c r="AG4" s="7" t="n">
-        <v>0.04628787878787879</v>
+        <v>-0.0196367206676485</v>
       </c>
       <c r="AH4" s="9" t="inlineStr">
         <is>
@@ -1525,72 +1522,45 @@
       <c r="L5" s="6" t="n">
         <v>592.6</v>
       </c>
-      <c r="M5" s="6" t="n">
-        <v>675.6</v>
-      </c>
       <c r="N5" s="6" t="n">
         <v>592.6</v>
       </c>
-      <c r="O5" s="6" t="n">
-        <v>699.3</v>
-      </c>
       <c r="P5" s="6" t="n">
         <v>622.2</v>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v>746.6</v>
-      </c>
       <c r="R5" s="6" t="n">
         <v>592.6</v>
       </c>
-      <c r="S5" s="6" t="n">
-        <v>711.1</v>
-      </c>
       <c r="T5" s="6" t="n">
         <v>592.6</v>
       </c>
-      <c r="U5" s="6" t="n">
-        <v>723</v>
-      </c>
       <c r="V5" s="6" t="n">
         <v>622.2</v>
       </c>
-      <c r="W5" s="6" t="n">
-        <v>771.5</v>
-      </c>
       <c r="X5" s="6" t="n">
         <v>592.6</v>
       </c>
-      <c r="Y5" s="6" t="n">
-        <v>740.8</v>
-      </c>
       <c r="Z5" s="6" t="n">
         <v>592.6</v>
       </c>
-      <c r="AA5" s="6" t="n">
-        <v>746.7</v>
-      </c>
       <c r="AB5" s="6" t="n">
         <v>622.2</v>
       </c>
-      <c r="AC5" s="6" t="n">
-        <v>796.4</v>
-      </c>
       <c r="AD5" s="6" t="n">
-        <v>7200</v>
+        <v>1777.8</v>
       </c>
       <c r="AE5" s="6" t="n">
-        <v>8549.4</v>
+        <v>1938.4</v>
       </c>
       <c r="AF5" s="6" t="n">
-        <v>1349.4</v>
+        <v>160.6</v>
       </c>
       <c r="AG5" s="7" t="n">
-        <v>0.1874166666666667</v>
+        <v>0.09033637079536505</v>
       </c>
       <c r="AH5" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Amber</t>
         </is>
       </c>
     </row>
@@ -1639,72 +1609,45 @@
       <c r="L6" s="6" t="n">
         <v>790.1</v>
       </c>
-      <c r="M6" s="6" t="n">
-        <v>853.3</v>
-      </c>
       <c r="N6" s="6" t="n">
         <v>790.1</v>
       </c>
-      <c r="O6" s="6" t="n">
-        <v>869.1</v>
-      </c>
       <c r="P6" s="6" t="n">
         <v>829.6</v>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v>937.4</v>
-      </c>
       <c r="R6" s="6" t="n">
         <v>790.1</v>
       </c>
-      <c r="S6" s="6" t="n">
-        <v>908.6</v>
-      </c>
       <c r="T6" s="6" t="n">
         <v>790.1</v>
       </c>
-      <c r="U6" s="6" t="n">
-        <v>932.3</v>
-      </c>
       <c r="V6" s="6" t="n">
         <v>829.6</v>
       </c>
-      <c r="W6" s="6" t="n">
-        <v>995.5</v>
-      </c>
       <c r="X6" s="6" t="n">
         <v>790.1</v>
       </c>
-      <c r="Y6" s="6" t="n">
-        <v>963.9</v>
-      </c>
       <c r="Z6" s="6" t="n">
         <v>790.1</v>
       </c>
-      <c r="AA6" s="6" t="n">
-        <v>987.6</v>
-      </c>
       <c r="AB6" s="6" t="n">
         <v>829.6</v>
       </c>
-      <c r="AC6" s="6" t="n">
-        <v>1061.9</v>
-      </c>
       <c r="AD6" s="6" t="n">
-        <v>9599.700000000001</v>
+        <v>2370.3</v>
       </c>
       <c r="AE6" s="6" t="n">
-        <v>10936.4</v>
+        <v>2426.8</v>
       </c>
       <c r="AF6" s="6" t="n">
-        <v>1336.7</v>
+        <v>56.5</v>
       </c>
       <c r="AG6" s="7" t="n">
-        <v>0.1392439347062929</v>
-      </c>
-      <c r="AH6" s="8" t="inlineStr">
-        <is>
-          <t>Red</t>
+        <v>0.0238366451504029</v>
+      </c>
+      <c r="AH6" s="9" t="inlineStr">
+        <is>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1753,70 +1696,43 @@
       <c r="L7" s="6" t="n">
         <v>987.7</v>
       </c>
-      <c r="M7" s="6" t="n">
-        <v>1037.1</v>
-      </c>
       <c r="N7" s="6" t="n">
         <v>987.7</v>
       </c>
-      <c r="O7" s="6" t="n">
-        <v>1047</v>
-      </c>
       <c r="P7" s="6" t="n">
         <v>1037</v>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v>1109.6</v>
-      </c>
       <c r="R7" s="6" t="n">
         <v>987.7</v>
       </c>
-      <c r="S7" s="6" t="n">
-        <v>1047</v>
-      </c>
       <c r="T7" s="6" t="n">
         <v>987.7</v>
       </c>
-      <c r="U7" s="6" t="n">
-        <v>1037.1</v>
-      </c>
       <c r="V7" s="6" t="n">
         <v>1037</v>
       </c>
-      <c r="W7" s="6" t="n">
-        <v>1099.2</v>
-      </c>
       <c r="X7" s="6" t="n">
         <v>987.7</v>
       </c>
-      <c r="Y7" s="6" t="n">
-        <v>1037.1</v>
-      </c>
       <c r="Z7" s="6" t="n">
         <v>987.7</v>
       </c>
-      <c r="AA7" s="6" t="n">
-        <v>1047</v>
-      </c>
       <c r="AB7" s="6" t="n">
         <v>1037</v>
       </c>
-      <c r="AC7" s="6" t="n">
-        <v>1088.9</v>
-      </c>
       <c r="AD7" s="6" t="n">
-        <v>12000.2</v>
+        <v>2963</v>
       </c>
       <c r="AE7" s="6" t="n">
-        <v>12661.6</v>
+        <v>3111.6</v>
       </c>
       <c r="AF7" s="6" t="n">
-        <v>661.4</v>
+        <v>148.6</v>
       </c>
       <c r="AG7" s="7" t="n">
-        <v>0.05511574807086548</v>
-      </c>
-      <c r="AH7" s="10" t="inlineStr">
+        <v>0.05015187310158623</v>
+      </c>
+      <c r="AH7" s="8" t="inlineStr">
         <is>
           <t>Amber</t>
         </is>
@@ -1867,68 +1783,41 @@
       <c r="L8" s="6" t="n">
         <v>395.1</v>
       </c>
-      <c r="M8" s="6" t="n">
-        <v>379.3</v>
-      </c>
       <c r="N8" s="6" t="n">
         <v>395.1</v>
       </c>
-      <c r="O8" s="6" t="n">
-        <v>383.2</v>
-      </c>
       <c r="P8" s="6" t="n">
         <v>414.8</v>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v>398.2</v>
-      </c>
       <c r="R8" s="6" t="n">
         <v>395.1</v>
       </c>
-      <c r="S8" s="6" t="n">
-        <v>375.3</v>
-      </c>
       <c r="T8" s="6" t="n">
         <v>395.1</v>
       </c>
-      <c r="U8" s="6" t="n">
-        <v>379.3</v>
-      </c>
       <c r="V8" s="6" t="n">
         <v>414.8</v>
       </c>
-      <c r="W8" s="6" t="n">
-        <v>402.4</v>
-      </c>
       <c r="X8" s="6" t="n">
         <v>395.1</v>
       </c>
-      <c r="Y8" s="6" t="n">
-        <v>379.3</v>
-      </c>
       <c r="Z8" s="6" t="n">
         <v>395.1</v>
       </c>
-      <c r="AA8" s="6" t="n">
-        <v>375.3</v>
-      </c>
       <c r="AB8" s="6" t="n">
         <v>414.8</v>
       </c>
-      <c r="AC8" s="6" t="n">
-        <v>398.2</v>
-      </c>
       <c r="AD8" s="6" t="n">
-        <v>4800.2</v>
+        <v>1185.2</v>
       </c>
       <c r="AE8" s="6" t="n">
-        <v>4608.5</v>
+        <v>1138</v>
       </c>
       <c r="AF8" s="6" t="n">
-        <v>-191.7</v>
+        <v>-47.2</v>
       </c>
       <c r="AG8" s="7" t="n">
-        <v>-0.03993583600683305</v>
+        <v>-0.03982450219372258</v>
       </c>
       <c r="AH8" s="9" t="inlineStr">
         <is>
@@ -1981,68 +1870,41 @@
       <c r="L9" s="6" t="n">
         <v>296.3</v>
       </c>
-      <c r="M9" s="6" t="n">
-        <v>296.3</v>
-      </c>
       <c r="N9" s="6" t="n">
         <v>296.3</v>
       </c>
-      <c r="O9" s="6" t="n">
-        <v>299.3</v>
-      </c>
       <c r="P9" s="6" t="n">
         <v>311.1</v>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v>311.1</v>
-      </c>
       <c r="R9" s="6" t="n">
         <v>296.3</v>
       </c>
-      <c r="S9" s="6" t="n">
-        <v>293.3</v>
-      </c>
       <c r="T9" s="6" t="n">
         <v>296.3</v>
       </c>
-      <c r="U9" s="6" t="n">
-        <v>296.3</v>
-      </c>
       <c r="V9" s="6" t="n">
         <v>311.1</v>
       </c>
-      <c r="W9" s="6" t="n">
-        <v>311.1</v>
-      </c>
       <c r="X9" s="6" t="n">
         <v>296.3</v>
       </c>
-      <c r="Y9" s="6" t="n">
-        <v>296.3</v>
-      </c>
       <c r="Z9" s="6" t="n">
         <v>296.3</v>
       </c>
-      <c r="AA9" s="6" t="n">
-        <v>296.3</v>
-      </c>
       <c r="AB9" s="6" t="n">
         <v>311.1</v>
       </c>
-      <c r="AC9" s="6" t="n">
-        <v>314.2</v>
-      </c>
       <c r="AD9" s="6" t="n">
-        <v>3600</v>
+        <v>888.9</v>
       </c>
       <c r="AE9" s="6" t="n">
-        <v>3594.4</v>
+        <v>880.2</v>
       </c>
       <c r="AF9" s="6" t="n">
-        <v>-5.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AG9" s="7" t="n">
-        <v>-0.001555555555555555</v>
+        <v>-0.009787377657779277</v>
       </c>
       <c r="AH9" s="9" t="inlineStr">
         <is>
@@ -2095,68 +1957,41 @@
       <c r="L10" s="6" t="n">
         <v>148.1</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>142.2</v>
-      </c>
       <c r="N10" s="6" t="n">
         <v>148.1</v>
       </c>
-      <c r="O10" s="6" t="n">
-        <v>140.7</v>
-      </c>
       <c r="P10" s="6" t="n">
         <v>155.6</v>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v>149.4</v>
-      </c>
       <c r="R10" s="6" t="n">
         <v>148.1</v>
       </c>
-      <c r="S10" s="6" t="n">
-        <v>143.7</v>
-      </c>
       <c r="T10" s="6" t="n">
         <v>148.1</v>
       </c>
-      <c r="U10" s="6" t="n">
-        <v>140.7</v>
-      </c>
       <c r="V10" s="6" t="n">
         <v>155.6</v>
       </c>
-      <c r="W10" s="6" t="n">
-        <v>149.4</v>
-      </c>
       <c r="X10" s="6" t="n">
         <v>148.1</v>
       </c>
-      <c r="Y10" s="6" t="n">
-        <v>142.2</v>
-      </c>
       <c r="Z10" s="6" t="n">
         <v>148.1</v>
       </c>
-      <c r="AA10" s="6" t="n">
-        <v>140.7</v>
-      </c>
       <c r="AB10" s="6" t="n">
         <v>155.6</v>
       </c>
-      <c r="AC10" s="6" t="n">
-        <v>146.3</v>
-      </c>
       <c r="AD10" s="6" t="n">
-        <v>1799.8</v>
+        <v>444.4</v>
       </c>
       <c r="AE10" s="6" t="n">
-        <v>1722.1</v>
+        <v>426.8</v>
       </c>
       <c r="AF10" s="6" t="n">
-        <v>-77.7</v>
+        <v>-17.6</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>-0.04317146349594399</v>
+        <v>-0.03960396039603961</v>
       </c>
       <c r="AH10" s="9" t="inlineStr">
         <is>
@@ -2209,70 +2044,43 @@
       <c r="L11" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>225.1</v>
-      </c>
       <c r="N11" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="O11" s="6" t="n">
-        <v>229.1</v>
-      </c>
       <c r="P11" s="6" t="n">
         <v>207.4</v>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v>244.7</v>
-      </c>
       <c r="R11" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="S11" s="6" t="n">
-        <v>237</v>
-      </c>
       <c r="T11" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="U11" s="6" t="n">
-        <v>240.9</v>
-      </c>
       <c r="V11" s="6" t="n">
         <v>207.4</v>
       </c>
-      <c r="W11" s="6" t="n">
-        <v>248.9</v>
-      </c>
       <c r="X11" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="Y11" s="6" t="n">
-        <v>233</v>
-      </c>
       <c r="Z11" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="AA11" s="6" t="n">
-        <v>229.1</v>
-      </c>
       <c r="AB11" s="6" t="n">
         <v>207.4</v>
       </c>
-      <c r="AC11" s="6" t="n">
-        <v>238.5</v>
-      </c>
       <c r="AD11" s="6" t="n">
-        <v>2399.8</v>
+        <v>592.6</v>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>2792.3</v>
+        <v>666</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>392.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>0.1635552962746895</v>
-      </c>
-      <c r="AH11" s="8" t="inlineStr">
+        <v>0.1238609517381033</v>
+      </c>
+      <c r="AH11" s="10" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -2323,72 +2131,45 @@
       <c r="L12" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="M12" s="6" t="n">
-        <v>283.9</v>
-      </c>
       <c r="N12" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="O12" s="6" t="n">
-        <v>291.3</v>
-      </c>
       <c r="P12" s="6" t="n">
         <v>259.3</v>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v>311.2</v>
-      </c>
       <c r="R12" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="S12" s="6" t="n">
-        <v>301.2</v>
-      </c>
       <c r="T12" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="U12" s="6" t="n">
-        <v>296.3</v>
-      </c>
       <c r="V12" s="6" t="n">
         <v>259.3</v>
       </c>
-      <c r="W12" s="6" t="n">
-        <v>306</v>
-      </c>
       <c r="X12" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="Y12" s="6" t="n">
-        <v>283.9</v>
-      </c>
       <c r="Z12" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="AA12" s="6" t="n">
-        <v>276.5</v>
-      </c>
       <c r="AB12" s="6" t="n">
         <v>259.3</v>
       </c>
-      <c r="AC12" s="6" t="n">
-        <v>285.2</v>
-      </c>
       <c r="AD12" s="6" t="n">
-        <v>3000.1</v>
+        <v>740.8</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>3443.2</v>
+        <v>807.7</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>443.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG12" s="7" t="n">
-        <v>0.1476950768307723</v>
+        <v>0.09030777537796977</v>
       </c>
       <c r="AH12" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Amber</t>
         </is>
       </c>
     </row>
@@ -2437,68 +2218,41 @@
       <c r="L13" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="M13" s="6" t="n">
-        <v>197.5</v>
-      </c>
       <c r="N13" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="O13" s="6" t="n">
-        <v>197.5</v>
-      </c>
       <c r="P13" s="6" t="n">
         <v>207.4</v>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v>209.5</v>
-      </c>
       <c r="R13" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="S13" s="6" t="n">
-        <v>197.5</v>
-      </c>
       <c r="T13" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="U13" s="6" t="n">
-        <v>197.5</v>
-      </c>
       <c r="V13" s="6" t="n">
         <v>207.4</v>
       </c>
-      <c r="W13" s="6" t="n">
-        <v>209.5</v>
-      </c>
       <c r="X13" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="Y13" s="6" t="n">
-        <v>197.5</v>
-      </c>
       <c r="Z13" s="6" t="n">
         <v>197.5</v>
       </c>
-      <c r="AA13" s="6" t="n">
-        <v>195.5</v>
-      </c>
       <c r="AB13" s="6" t="n">
         <v>207.4</v>
       </c>
-      <c r="AC13" s="6" t="n">
-        <v>207.4</v>
-      </c>
       <c r="AD13" s="6" t="n">
-        <v>2399.8</v>
+        <v>592.6</v>
       </c>
       <c r="AE13" s="6" t="n">
-        <v>2396.1</v>
+        <v>586.7</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>-3.7</v>
+        <v>-5.9</v>
       </c>
       <c r="AG13" s="7" t="n">
-        <v>-0.0015417951495958</v>
+        <v>-0.009956125548430644</v>
       </c>
       <c r="AH13" s="9" t="inlineStr">
         <is>
@@ -2634,6 +2388,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3172,5 +2929,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/files/01_Rivanta_TechBudgetVariance.xlsx
+++ b/files/01_Rivanta_TechBudgetVariance.xlsx
@@ -625,7 +625,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reporting period: Q1 FY2026 (1 Jan – 31 Mar 2026). FY2026 full-year budget shown for context.</t>
+          <t>Reporting period: H1 FY2026 (1 Jan – 30 Jun 2026). FY2026 full-year budget shown for context.</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,21 @@
       <c r="L2" s="6" t="n">
         <v>2370.4</v>
       </c>
+      <c r="M2" s="6" t="n">
+        <v>2607.4</v>
+      </c>
       <c r="N2" s="6" t="n">
         <v>2370.4</v>
       </c>
+      <c r="O2" s="6" t="n">
+        <v>2702.3</v>
+      </c>
       <c r="P2" s="6" t="n">
         <v>2488.9</v>
       </c>
+      <c r="Q2" s="6" t="n">
+        <v>2936.9</v>
+      </c>
       <c r="R2" s="6" t="n">
         <v>2370.4</v>
       </c>
@@ -1286,16 +1295,16 @@
         <v>2488.9</v>
       </c>
       <c r="AD2" s="6" t="n">
-        <v>7111.2</v>
+        <v>14340.9</v>
       </c>
       <c r="AE2" s="6" t="n">
-        <v>7470.3</v>
+        <v>15716.9</v>
       </c>
       <c r="AF2" s="6" t="n">
-        <v>359.1</v>
+        <v>1376</v>
       </c>
       <c r="AG2" s="7" t="n">
-        <v>0.05049780627742154</v>
+        <v>0.09594934766995099</v>
       </c>
       <c r="AH2" s="8" t="inlineStr">
         <is>
@@ -1348,12 +1357,21 @@
       <c r="L3" s="6" t="n">
         <v>691.4</v>
       </c>
+      <c r="M3" s="6" t="n">
+        <v>719.1</v>
+      </c>
       <c r="N3" s="6" t="n">
         <v>691.4</v>
       </c>
+      <c r="O3" s="6" t="n">
+        <v>726</v>
+      </c>
       <c r="P3" s="6" t="n">
         <v>725.9</v>
       </c>
+      <c r="Q3" s="6" t="n">
+        <v>769.5</v>
+      </c>
       <c r="R3" s="6" t="n">
         <v>691.4</v>
       </c>
@@ -1373,16 +1391,16 @@
         <v>725.9</v>
       </c>
       <c r="AD3" s="6" t="n">
-        <v>2074.1</v>
+        <v>4182.8</v>
       </c>
       <c r="AE3" s="6" t="n">
-        <v>2074.8</v>
+        <v>4289.4</v>
       </c>
       <c r="AF3" s="6" t="n">
-        <v>0.7</v>
+        <v>106.6</v>
       </c>
       <c r="AG3" s="7" t="n">
-        <v>0.0003374957813027337</v>
+        <v>0.02548532083771636</v>
       </c>
       <c r="AH3" s="9" t="inlineStr">
         <is>
@@ -1435,12 +1453,21 @@
       <c r="L4" s="6" t="n">
         <v>543.2</v>
       </c>
+      <c r="M4" s="6" t="n">
+        <v>554.1</v>
+      </c>
       <c r="N4" s="6" t="n">
         <v>543.2</v>
       </c>
+      <c r="O4" s="6" t="n">
+        <v>564.9</v>
+      </c>
       <c r="P4" s="6" t="n">
         <v>570.4</v>
       </c>
+      <c r="Q4" s="6" t="n">
+        <v>598.9</v>
+      </c>
       <c r="R4" s="6" t="n">
         <v>543.2</v>
       </c>
@@ -1460,16 +1487,16 @@
         <v>570.4</v>
       </c>
       <c r="AD4" s="6" t="n">
-        <v>1629.6</v>
+        <v>3286.4</v>
       </c>
       <c r="AE4" s="6" t="n">
-        <v>1597.6</v>
+        <v>3315.5</v>
       </c>
       <c r="AF4" s="6" t="n">
-        <v>-32</v>
+        <v>29.1</v>
       </c>
       <c r="AG4" s="7" t="n">
-        <v>-0.0196367206676485</v>
+        <v>0.008854673807205452</v>
       </c>
       <c r="AH4" s="9" t="inlineStr">
         <is>
@@ -1522,12 +1549,21 @@
       <c r="L5" s="6" t="n">
         <v>592.6</v>
       </c>
+      <c r="M5" s="6" t="n">
+        <v>675.6</v>
+      </c>
       <c r="N5" s="6" t="n">
         <v>592.6</v>
       </c>
+      <c r="O5" s="6" t="n">
+        <v>699.3</v>
+      </c>
       <c r="P5" s="6" t="n">
         <v>622.2</v>
       </c>
+      <c r="Q5" s="6" t="n">
+        <v>746.6</v>
+      </c>
       <c r="R5" s="6" t="n">
         <v>592.6</v>
       </c>
@@ -1547,20 +1583,20 @@
         <v>622.2</v>
       </c>
       <c r="AD5" s="6" t="n">
-        <v>1777.8</v>
+        <v>3585.2</v>
       </c>
       <c r="AE5" s="6" t="n">
-        <v>1938.4</v>
+        <v>4059.9</v>
       </c>
       <c r="AF5" s="6" t="n">
-        <v>160.6</v>
+        <v>474.7</v>
       </c>
       <c r="AG5" s="7" t="n">
-        <v>0.09033637079536505</v>
-      </c>
-      <c r="AH5" s="8" t="inlineStr">
-        <is>
-          <t>Amber</t>
+        <v>0.1324054446056008</v>
+      </c>
+      <c r="AH5" s="10" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1645,21 @@
       <c r="L6" s="6" t="n">
         <v>790.1</v>
       </c>
+      <c r="M6" s="6" t="n">
+        <v>853.3</v>
+      </c>
       <c r="N6" s="6" t="n">
         <v>790.1</v>
       </c>
+      <c r="O6" s="6" t="n">
+        <v>869.1</v>
+      </c>
       <c r="P6" s="6" t="n">
         <v>829.6</v>
       </c>
+      <c r="Q6" s="6" t="n">
+        <v>937.4</v>
+      </c>
       <c r="R6" s="6" t="n">
         <v>790.1</v>
       </c>
@@ -1634,20 +1679,20 @@
         <v>829.6</v>
       </c>
       <c r="AD6" s="6" t="n">
-        <v>2370.3</v>
+        <v>4780.1</v>
       </c>
       <c r="AE6" s="6" t="n">
-        <v>2426.8</v>
+        <v>5086.6</v>
       </c>
       <c r="AF6" s="6" t="n">
-        <v>56.5</v>
+        <v>306.5</v>
       </c>
       <c r="AG6" s="7" t="n">
-        <v>0.0238366451504029</v>
-      </c>
-      <c r="AH6" s="9" t="inlineStr">
-        <is>
-          <t>Green</t>
+        <v>0.06411999748959227</v>
+      </c>
+      <c r="AH6" s="8" t="inlineStr">
+        <is>
+          <t>Amber</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1741,21 @@
       <c r="L7" s="6" t="n">
         <v>987.7</v>
       </c>
+      <c r="M7" s="6" t="n">
+        <v>1037.1</v>
+      </c>
       <c r="N7" s="6" t="n">
         <v>987.7</v>
       </c>
+      <c r="O7" s="6" t="n">
+        <v>1047</v>
+      </c>
       <c r="P7" s="6" t="n">
         <v>1037</v>
       </c>
+      <c r="Q7" s="6" t="n">
+        <v>1109.6</v>
+      </c>
       <c r="R7" s="6" t="n">
         <v>987.7</v>
       </c>
@@ -1721,16 +1775,16 @@
         <v>1037</v>
       </c>
       <c r="AD7" s="6" t="n">
-        <v>2963</v>
+        <v>5975.4</v>
       </c>
       <c r="AE7" s="6" t="n">
-        <v>3111.6</v>
+        <v>6305.3</v>
       </c>
       <c r="AF7" s="6" t="n">
-        <v>148.6</v>
+        <v>329.9</v>
       </c>
       <c r="AG7" s="7" t="n">
-        <v>0.05015187310158623</v>
+        <v>0.05520969307494059</v>
       </c>
       <c r="AH7" s="8" t="inlineStr">
         <is>
@@ -1783,12 +1837,21 @@
       <c r="L8" s="6" t="n">
         <v>395.1</v>
       </c>
+      <c r="M8" s="6" t="n">
+        <v>379.3</v>
+      </c>
       <c r="N8" s="6" t="n">
         <v>395.1</v>
       </c>
+      <c r="O8" s="6" t="n">
+        <v>383.2</v>
+      </c>
       <c r="P8" s="6" t="n">
         <v>414.8</v>
       </c>
+      <c r="Q8" s="6" t="n">
+        <v>398.2</v>
+      </c>
       <c r="R8" s="6" t="n">
         <v>395.1</v>
       </c>
@@ -1808,16 +1871,16 @@
         <v>414.8</v>
       </c>
       <c r="AD8" s="6" t="n">
-        <v>1185.2</v>
+        <v>2390.2</v>
       </c>
       <c r="AE8" s="6" t="n">
-        <v>1138</v>
+        <v>2298.7</v>
       </c>
       <c r="AF8" s="6" t="n">
-        <v>-47.2</v>
+        <v>-91.5</v>
       </c>
       <c r="AG8" s="7" t="n">
-        <v>-0.03982450219372258</v>
+        <v>-0.03828131537109866</v>
       </c>
       <c r="AH8" s="9" t="inlineStr">
         <is>
@@ -1870,12 +1933,21 @@
       <c r="L9" s="6" t="n">
         <v>296.3</v>
       </c>
+      <c r="M9" s="6" t="n">
+        <v>296.3</v>
+      </c>
       <c r="N9" s="6" t="n">
         <v>296.3</v>
       </c>
+      <c r="O9" s="6" t="n">
+        <v>299.3</v>
+      </c>
       <c r="P9" s="6" t="n">
         <v>311.1</v>
       </c>
+      <c r="Q9" s="6" t="n">
+        <v>311.1</v>
+      </c>
       <c r="R9" s="6" t="n">
         <v>296.3</v>
       </c>
@@ -1895,16 +1967,16 @@
         <v>311.1</v>
       </c>
       <c r="AD9" s="6" t="n">
-        <v>888.9</v>
+        <v>1792.6</v>
       </c>
       <c r="AE9" s="6" t="n">
-        <v>880.2</v>
+        <v>1786.9</v>
       </c>
       <c r="AF9" s="6" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.7</v>
       </c>
       <c r="AG9" s="7" t="n">
-        <v>-0.009787377657779277</v>
+        <v>-0.00317973892669865</v>
       </c>
       <c r="AH9" s="9" t="inlineStr">
         <is>
@@ -1957,12 +2029,21 @@
       <c r="L10" s="6" t="n">
         <v>148.1</v>
       </c>
+      <c r="M10" s="6" t="n">
+        <v>142.2</v>
+      </c>
       <c r="N10" s="6" t="n">
         <v>148.1</v>
       </c>
+      <c r="O10" s="6" t="n">
+        <v>140.7</v>
+      </c>
       <c r="P10" s="6" t="n">
         <v>155.6</v>
       </c>
+      <c r="Q10" s="6" t="n">
+        <v>149.4</v>
+      </c>
       <c r="R10" s="6" t="n">
         <v>148.1</v>
       </c>
@@ -1982,16 +2063,16 @@
         <v>155.6</v>
       </c>
       <c r="AD10" s="6" t="n">
-        <v>444.4</v>
+        <v>896.2</v>
       </c>
       <c r="AE10" s="6" t="n">
-        <v>426.8</v>
+        <v>859.1</v>
       </c>
       <c r="AF10" s="6" t="n">
-        <v>-17.6</v>
+        <v>-37.1</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>-0.03960396039603961</v>
+        <v>-0.04139700959607231</v>
       </c>
       <c r="AH10" s="9" t="inlineStr">
         <is>
@@ -2044,12 +2125,21 @@
       <c r="L11" s="6" t="n">
         <v>197.5</v>
       </c>
+      <c r="M11" s="6" t="n">
+        <v>225.1</v>
+      </c>
       <c r="N11" s="6" t="n">
         <v>197.5</v>
       </c>
+      <c r="O11" s="6" t="n">
+        <v>229.1</v>
+      </c>
       <c r="P11" s="6" t="n">
         <v>207.4</v>
       </c>
+      <c r="Q11" s="6" t="n">
+        <v>244.7</v>
+      </c>
       <c r="R11" s="6" t="n">
         <v>197.5</v>
       </c>
@@ -2069,16 +2159,16 @@
         <v>207.4</v>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>592.6</v>
+        <v>1195</v>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>666</v>
+        <v>1364.9</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>73.40000000000001</v>
+        <v>169.9</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>0.1238609517381033</v>
+        <v>0.1421757322175732</v>
       </c>
       <c r="AH11" s="10" t="inlineStr">
         <is>
@@ -2131,12 +2221,21 @@
       <c r="L12" s="6" t="n">
         <v>246.9</v>
       </c>
+      <c r="M12" s="6" t="n">
+        <v>283.9</v>
+      </c>
       <c r="N12" s="6" t="n">
         <v>246.9</v>
       </c>
+      <c r="O12" s="6" t="n">
+        <v>291.3</v>
+      </c>
       <c r="P12" s="6" t="n">
         <v>259.3</v>
       </c>
+      <c r="Q12" s="6" t="n">
+        <v>311.2</v>
+      </c>
       <c r="R12" s="6" t="n">
         <v>246.9</v>
       </c>
@@ -2156,20 +2255,20 @@
         <v>259.3</v>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>740.8</v>
+        <v>1493.9</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>807.7</v>
+        <v>1694.1</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>66.90000000000001</v>
+        <v>200.2</v>
       </c>
       <c r="AG12" s="7" t="n">
-        <v>0.09030777537796977</v>
-      </c>
-      <c r="AH12" s="8" t="inlineStr">
-        <is>
-          <t>Amber</t>
+        <v>0.1340116473659549</v>
+      </c>
+      <c r="AH12" s="10" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2317,21 @@
       <c r="L13" s="6" t="n">
         <v>197.5</v>
       </c>
+      <c r="M13" s="6" t="n">
+        <v>197.5</v>
+      </c>
       <c r="N13" s="6" t="n">
         <v>197.5</v>
       </c>
+      <c r="O13" s="6" t="n">
+        <v>197.5</v>
+      </c>
       <c r="P13" s="6" t="n">
         <v>207.4</v>
       </c>
+      <c r="Q13" s="6" t="n">
+        <v>209.5</v>
+      </c>
       <c r="R13" s="6" t="n">
         <v>197.5</v>
       </c>
@@ -2243,16 +2351,16 @@
         <v>207.4</v>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>592.6</v>
+        <v>1195</v>
       </c>
       <c r="AE13" s="6" t="n">
-        <v>586.7</v>
+        <v>1191.2</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>-5.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AG13" s="7" t="n">
-        <v>-0.009956125548430644</v>
+        <v>-0.003179916317991632</v>
       </c>
       <c r="AH13" s="9" t="inlineStr">
         <is>
